--- a/results/link-prediction-gcn/Link/3shot/MUTAG/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/3shot/MUTAG/GCN_total_results.xlsx
@@ -898,62 +898,62 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.6607±0.0000</t>
+          <t>0.7380±0.0215</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6147±0.0710</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.6905±0.0000</t>
+          <t>0.6673±0.0055</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6705±0.0191</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.6625±0.0000</t>
+          <t>0.7028±0.0062</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.6625±0.0000</t>
+          <t>0.7082±0.0359</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.6625±0.0000</t>
+          <t>0.7165±0.0142</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.6625±0.0000</t>
+          <t>0.7165±0.0142</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.6625±0.0000</t>
+          <t>0.7165±0.0142</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.6625±0.0000</t>
+          <t>0.6834±0.0298</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.7375±0.0000</t>
+          <t>0.6842±0.0400</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.7247±0.0212</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -963,62 +963,62 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6713±0.0218</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6637±0.0008</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.6750±0.0000</t>
+          <t>0.6583±0.0069</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6701±0.0206</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6607±0.0072</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.6625±0.0000</t>
+          <t>0.6712±0.0067</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6619±0.0055</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6619±0.0055</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6619±0.0055</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.6661±0.0000</t>
+          <t>0.6836±0.0140</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.6268±0.0000</t>
+          <t>0.6955±0.0040</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.6589±0.0000</t>
+          <t>0.6911±0.0183</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1028,62 +1028,62 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.4973±0.0000</t>
+          <t>0.5598±0.0828</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.5607±0.0000</t>
+          <t>0.5307±0.0365</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.5492±0.0000</t>
+          <t>0.5861±0.0457</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.7086±0.0223</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.5375±0.0000</t>
+          <t>0.5923±0.0473</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.4973±0.0000</t>
+          <t>0.7078±0.0208</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.5107±0.0000</t>
+          <t>0.5862±0.0624</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.5107±0.0000</t>
+          <t>0.5862±0.0624</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.5107±0.0000</t>
+          <t>0.5862±0.0624</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.5107±0.0000</t>
+          <t>0.7281±0.0087</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.5474±0.0000</t>
+          <t>0.5164±0.0259</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.5170±0.0000</t>
+          <t>0.6687±0.0388</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1093,62 +1093,62 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.7030±0.0000</t>
+          <t>0.6802±0.0459</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.5957±0.0000</t>
+          <t>0.6506±0.0169</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.6250±0.0000</t>
+          <t>0.6757±0.0487</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6629±0.0183</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.6869±0.0000</t>
+          <t>0.7118±0.0058</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.7138±0.0000</t>
+          <t>0.7191±0.0022</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.7174±0.0000</t>
+          <t>0.7156±0.0038</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.7174±0.0000</t>
+          <t>0.7156±0.0038</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.7174±0.0000</t>
+          <t>0.7156±0.0038</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.7245±0.0000</t>
+          <t>0.7168±0.0071</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.7036±0.0000</t>
+          <t>0.6977±0.0313</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.7143±0.0000</t>
+          <t>0.7209±0.0064</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
@@ -1158,62 +1158,62 @@
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.6571±0.0000</t>
+          <t>0.6973±0.0039</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.6589±0.0000</t>
+          <t>0.6251±0.0126</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.6089±0.0000</t>
+          <t>0.6277±0.0173</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.7232±0.0000</t>
+          <t>0.6426±0.0463</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.6607±0.0000</t>
+          <t>0.6889±0.0028</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.6625±0.0000</t>
+          <t>0.6913±0.0087</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.6762±0.0000</t>
+          <t>0.6919±0.0042</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.6762±0.0000</t>
+          <t>0.6919±0.0042</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.6762±0.0000</t>
+          <t>0.6919±0.0042</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.6143±0.0000</t>
+          <t>0.6656±0.0235</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.7161±0.0000</t>
+          <t>0.6504±0.0253</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.6625±0.0000</t>
+          <t>0.6828±0.0134</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
@@ -1223,62 +1223,62 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0.6839±0.0000</t>
+          <t>0.6615±0.0251</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.6679±0.0000</t>
+          <t>0.6371±0.0176</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.6357±0.0000</t>
+          <t>0.6327±0.0075</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.7143±0.0000</t>
+          <t>0.6726±0.0362</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.6780±0.0000</t>
+          <t>0.6831±0.0127</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.6571±0.0000</t>
+          <t>0.6573±0.0211</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6434±0.0085</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6434±0.0085</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6434±0.0085</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.6571±0.0000</t>
+          <t>0.6579±0.0170</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.7143±0.0000</t>
+          <t>0.6810±0.0201</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6726±0.0241</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
@@ -1288,62 +1288,62 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.6679±0.0000</t>
+          <t>0.6315±0.0143</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.5993±0.0000</t>
+          <t>0.6589±0.0372</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.6089±0.0000</t>
+          <t>0.6420±0.0323</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6623±0.0037</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.6589±0.0000</t>
+          <t>0.6774±0.0043</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.6054±0.0000</t>
+          <t>0.6699±0.0198</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.6816±0.0000</t>
+          <t>0.6746±0.0348</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.6816±0.0000</t>
+          <t>0.6746±0.0348</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.6816±0.0000</t>
+          <t>0.6746±0.0348</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.6018±0.0000</t>
+          <t>0.6502±0.0138</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.6214±0.0000</t>
+          <t>0.6327±0.0148</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.6589±0.0000</t>
+          <t>0.6987±0.0007</t>
         </is>
       </c>
     </row>
@@ -1360,62 +1360,62 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.7957±0.0000</t>
+          <t>0.8168±0.0150</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7355±0.0893</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.8014±0.0000</t>
+          <t>0.7984±0.0033</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7853±0.0165</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.7966±0.0000</t>
+          <t>0.7977±0.0055</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.7966±0.0000</t>
+          <t>0.7904±0.0304</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.7966±0.0000</t>
+          <t>0.8035±0.0092</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.7966±0.0000</t>
+          <t>0.8035±0.0092</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.7966±0.0000</t>
+          <t>0.8035±0.0092</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.7970±0.0000</t>
+          <t>0.7781±0.0273</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.8178±0.0000</t>
+          <t>0.7696±0.0369</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.8095±0.0131</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1425,62 +1425,62 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7941±0.0044</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7979±0.0006</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.7889±0.0000</t>
+          <t>0.7932±0.0045</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7960±0.0081</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7926±0.0095</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.7970±0.0000</t>
+          <t>0.7790±0.0137</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7949±0.0040</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7949±0.0040</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7949±0.0040</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.7991±0.0000</t>
+          <t>0.7877±0.0122</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.7164±0.0000</t>
+          <t>0.7821±0.0098</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.7944±0.0000</t>
+          <t>0.8077±0.0061</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1490,62 +1490,62 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.5723±0.0000</t>
+          <t>0.6386±0.0904</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.7099±0.0000</t>
+          <t>0.6398±0.0493</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.6480±0.0000</t>
+          <t>0.6944±0.0244</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7985±0.0129</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.6163±0.0000</t>
+          <t>0.6848±0.0560</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.5630±0.0000</t>
+          <t>0.7918±0.0172</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.5595±0.0000</t>
+          <t>0.6734±0.0762</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.5595±0.0000</t>
+          <t>0.6734±0.0762</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.5595±0.0000</t>
+          <t>0.6734±0.0762</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.5581±0.0000</t>
+          <t>0.8118±0.0073</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.6970±0.0000</t>
+          <t>0.5757±0.0201</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.5934±0.0000</t>
+          <t>0.7571±0.0345</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1555,62 +1555,62 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.7899±0.0000</t>
+          <t>0.7761±0.0410</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.7438±0.0000</t>
+          <t>0.7644±0.0283</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.7273±0.0000</t>
+          <t>0.7712±0.0375</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7653±0.0159</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.7831±0.0000</t>
+          <t>0.8072±0.0032</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.8015±0.0000</t>
+          <t>0.8087±0.0049</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.8035±0.0000</t>
+          <t>0.8088±0.0026</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.8035±0.0000</t>
+          <t>0.8088±0.0026</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.8035±0.0000</t>
+          <t>0.8088±0.0026</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>0.8080±0.0000</t>
+          <t>0.8071±0.0049</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.7877±0.0000</t>
+          <t>0.7826±0.0307</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.8015±0.0000</t>
+          <t>0.8116±0.0040</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1620,62 +1620,62 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>0.7563±0.0000</t>
+          <t>0.7947±0.0018</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.7917±0.0000</t>
+          <t>0.7264±0.0083</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.7181±0.0000</t>
+          <t>0.7211±0.0124</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>0.8093±0.0000</t>
+          <t>0.7448±0.0440</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.7607±0.0000</t>
+          <t>0.7885±0.0019</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.7623±0.0000</t>
+          <t>0.7870±0.0051</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>0.7712±0.0000</t>
+          <t>0.7903±0.0032</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>0.7712±0.0000</t>
+          <t>0.7903±0.0032</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>0.7712±0.0000</t>
+          <t>0.7903±0.0032</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.7150±0.0000</t>
+          <t>0.7636±0.0208</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.8049±0.0000</t>
+          <t>0.7412±0.0243</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0.7586±0.0000</t>
+          <t>0.7920±0.0061</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -1685,62 +1685,62 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>0.7834±0.0000</t>
+          <t>0.7660±0.0269</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0.7978±0.0000</t>
+          <t>0.7375±0.0146</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.7424±0.0000</t>
+          <t>0.7256±0.0055</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.8049±0.0000</t>
+          <t>0.7709±0.0343</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.7767±0.0000</t>
+          <t>0.7799±0.0134</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.7545±0.0000</t>
+          <t>0.7589±0.0272</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.7626±0.0000</t>
+          <t>0.7566±0.0138</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.7626±0.0000</t>
+          <t>0.7566±0.0138</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>0.7626±0.0000</t>
+          <t>0.7566±0.0138</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.7545±0.0000</t>
+          <t>0.7576±0.0227</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.8034±0.0000</t>
+          <t>0.7683±0.0161</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>0.7620±0.0000</t>
+          <t>0.7819±0.0045</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
@@ -1750,62 +1750,62 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.7698±0.0000</t>
+          <t>0.7334±0.0096</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.7472±0.0000</t>
+          <t>0.7842±0.0174</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.7115±0.0000</t>
+          <t>0.7394±0.0358</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.7983±0.0000</t>
+          <t>0.7864±0.0174</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.7615±0.0000</t>
+          <t>0.7827±0.0052</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.7119±0.0000</t>
+          <t>0.7727±0.0176</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.7792±0.0000</t>
+          <t>0.7761±0.0295</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.7792±0.0000</t>
+          <t>0.7761±0.0295</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.7792±0.0000</t>
+          <t>0.7761±0.0295</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.7130±0.0000</t>
+          <t>0.7565±0.0155</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.7039±0.0000</t>
+          <t>0.7244±0.0133</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.7633±0.0000</t>
+          <t>0.7958±0.0006</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.7132±0.0000</t>
+          <t>0.7619±0.0152</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.5321±0.0000</t>
+          <t>0.6255±0.0397</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.3650±0.0000</t>
+          <t>0.4471±0.0701</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.6384±0.0000</t>
+          <t>0.6271±0.0274</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.6031±0.0000</t>
+          <t>0.5726±0.0101</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.5286±0.0000</t>
+          <t>0.5674±0.0160</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.5313±0.0000</t>
+          <t>0.6229±0.0356</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.5322±0.0000</t>
+          <t>0.5940±0.0203</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.5322±0.0000</t>
+          <t>0.5940±0.0203</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.5322±0.0000</t>
+          <t>0.5940±0.0203</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.5418±0.0000</t>
+          <t>0.5848±0.0065</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.6238±0.0000</t>
+          <t>0.6462±0.0136</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.5870±0.0000</t>
+          <t>0.6308±0.0224</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.4927±0.0000</t>
+          <t>0.7447±0.0320</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.6071±0.0000</t>
+          <t>0.5967±0.0364</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.5084±0.0000</t>
+          <t>0.5052±0.0333</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.6222±0.0000</t>
+          <t>0.6714±0.0157</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.5577±0.0000</t>
+          <t>0.5840±0.0805</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.6016±0.0000</t>
+          <t>0.5884±0.0357</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.6109±0.0000</t>
+          <t>0.6374±0.0182</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.6146±0.0000</t>
+          <t>0.6028±0.0175</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.6146±0.0000</t>
+          <t>0.6028±0.0175</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.6146±0.0000</t>
+          <t>0.6028±0.0175</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.6455±0.0000</t>
+          <t>0.6312±0.0271</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.5965±0.0000</t>
+          <t>0.6583±0.0327</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.5946±0.0000</t>
+          <t>0.6218±0.0208</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.5606±0.0000</t>
+          <t>0.7727±0.0124</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.4181±0.0000</t>
+          <t>0.5432±0.0643</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.2690±0.0000</t>
+          <t>0.4939±0.0018</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.4675±0.0000</t>
+          <t>0.4752±0.0299</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.4683±0.0000</t>
+          <t>0.5677±0.0392</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.4372±0.0000</t>
+          <t>0.5073±0.0155</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.4095±0.0000</t>
+          <t>0.5951±0.0300</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.4475±0.0000</t>
+          <t>0.5147±0.0435</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.4475±0.0000</t>
+          <t>0.5147±0.0435</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.4475±0.0000</t>
+          <t>0.5147±0.0435</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.4454±0.0000</t>
+          <t>0.5849±0.0085</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.4679±0.0000</t>
+          <t>0.5230±0.0217</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.4400±0.0000</t>
+          <t>0.5904±0.0271</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.7729±0.0000</t>
+          <t>0.7120±0.0464</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.6077±0.0000</t>
+          <t>0.5822±0.0319</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.4527±0.0000</t>
+          <t>0.5099±0.0129</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.6116±0.0000</t>
+          <t>0.6442±0.0082</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5574±0.0399</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.5854±0.0000</t>
+          <t>0.6216±0.0101</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.5971±0.0000</t>
+          <t>0.6004±0.0061</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.6438±0.0000</t>
+          <t>0.6394±0.0065</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.6438±0.0000</t>
+          <t>0.6394±0.0065</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.6438±0.0000</t>
+          <t>0.6394±0.0065</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.5808±0.0000</t>
+          <t>0.5992±0.0055</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.6480±0.0000</t>
+          <t>0.6469±0.0024</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.6396±0.0000</t>
+          <t>0.6426±0.0057</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.6705±0.0000</t>
+          <t>0.7725±0.0003</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.5781±0.0000</t>
+          <t>0.6045±0.0137</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.3135±0.0000</t>
+          <t>0.5795±0.0179</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.5359±0.0000</t>
+          <t>0.6561±0.0251</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.6400±0.0000</t>
+          <t>0.5952±0.0047</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.5836±0.0000</t>
+          <t>0.6132±0.0116</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.5838±0.0000</t>
+          <t>0.6207±0.0089</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.6056±0.0000</t>
+          <t>0.6146±0.0118</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.6056±0.0000</t>
+          <t>0.6146±0.0119</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.6056±0.0000</t>
+          <t>0.6146±0.0118</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.5821±0.0000</t>
+          <t>0.6135±0.0055</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.6193±0.0000</t>
+          <t>0.6257±0.0140</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.5940±0.0000</t>
+          <t>0.6274±0.0098</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.7130±0.0000</t>
+          <t>0.7729±0.0102</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.5776±0.0000</t>
+          <t>0.6081±0.0087</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.3009±0.0000</t>
+          <t>0.5862±0.0156</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.5495±0.0000</t>
+          <t>0.6178±0.0163</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.6164±0.0000</t>
+          <t>0.6150±0.0125</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.5948±0.0000</t>
+          <t>0.6127±0.0071</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.5779±0.0000</t>
+          <t>0.6103±0.0092</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.5750±0.0000</t>
+          <t>0.5973±0.0039</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.5750±0.0000</t>
+          <t>0.5973±0.0039</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.5750±0.0000</t>
+          <t>0.5973±0.0039</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.5779±0.0000</t>
+          <t>0.6056±0.0139</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.6151±0.0000</t>
+          <t>0.6440±0.0244</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.5879±0.0000</t>
+          <t>0.6174±0.0061</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.7327±0.0000</t>
+          <t>0.7828±0.0292</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.5281±0.0000</t>
+          <t>0.5731±0.0382</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.4556±0.0000</t>
+          <t>0.5266±0.0671</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.5652±0.0000</t>
+          <t>0.5928±0.0088</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5267±0.0377</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.5851±0.0000</t>
+          <t>0.5840±0.0095</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.5237±0.0000</t>
+          <t>0.5563±0.0251</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.5882±0.0000</t>
+          <t>0.5925±0.0252</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.5882±0.0000</t>
+          <t>0.5925±0.0252</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.5882±0.0000</t>
+          <t>0.5925±0.0252</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.5155±0.0000</t>
+          <t>0.5547±0.0253</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.6156±0.0000</t>
+          <t>0.6017±0.0242</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.5623±0.0000</t>
+          <t>0.6122±0.0012</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.8020±0.0000</t>
+          <t>0.8384±0.0016</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.6462±0.0000</t>
+          <t>0.7336±0.0167</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5597±0.0000</t>
+          <t>0.6448±0.0408</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.7290±0.0000</t>
+          <t>0.7369±0.0205</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.6742±0.0000</t>
+          <t>0.6964±0.0231</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.6452±0.0000</t>
+          <t>0.6859±0.0304</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.6469±0.0000</t>
+          <t>0.7306±0.0179</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.6475±0.0000</t>
+          <t>0.7305±0.0120</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.6475±0.0000</t>
+          <t>0.7305±0.0120</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.6475±0.0000</t>
+          <t>0.7305±0.0120</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.6600±0.0000</t>
+          <t>0.7094±0.0047</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.7352±0.0000</t>
+          <t>0.7415±0.0044</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.7014±0.0000</t>
+          <t>0.7317±0.0127</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.6374±0.0000</t>
+          <t>0.8386±0.0182</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.7209±0.0000</t>
+          <t>0.7028±0.0202</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.6480±0.0000</t>
+          <t>0.6643±0.0122</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.7456±0.0000</t>
+          <t>0.7969±0.0188</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.7125±0.0000</t>
+          <t>0.7152±0.0445</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.7114±0.0000</t>
+          <t>0.7194±0.0326</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.7086±0.0000</t>
+          <t>0.7511±0.0127</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.7078±0.0000</t>
+          <t>0.7198±0.0281</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7078±0.0000</t>
+          <t>0.7197±0.0281</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.7078±0.0000</t>
+          <t>0.7197±0.0281</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.7439±0.0000</t>
+          <t>0.7541±0.0225</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.7023±0.0000</t>
+          <t>0.7551±0.0216</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.7077±0.0000</t>
+          <t>0.7246±0.0163</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.6840±0.0000</t>
+          <t>0.8538±0.0117</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.6110±0.0000</t>
+          <t>0.6862±0.0335</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.5266±0.0000</t>
+          <t>0.6380±0.0108</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.6374±0.0000</t>
+          <t>0.6229±0.0105</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.6370±0.0000</t>
+          <t>0.6691±0.0242</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.6246±0.0000</t>
+          <t>0.6466±0.0121</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.6078±0.0000</t>
+          <t>0.7034±0.0197</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.6335±0.0000</t>
+          <t>0.6498±0.0194</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.6336±0.0000</t>
+          <t>0.6498±0.0193</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.6335±0.0000</t>
+          <t>0.6498±0.0193</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.6358±0.0000</t>
+          <t>0.7129±0.0058</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.6910±0.0000</t>
+          <t>0.6960±0.0276</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.6248±0.0000</t>
+          <t>0.6848±0.0186</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.8661±0.0000</t>
+          <t>0.8049±0.0346</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.7231±0.0000</t>
+          <t>0.7059±0.0276</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.6450±0.0000</t>
+          <t>0.6890±0.0165</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.7356±0.0000</t>
+          <t>0.7549±0.0018</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6986±0.0213</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.7099±0.0000</t>
+          <t>0.7312±0.0065</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.6946±0.0000</t>
+          <t>0.7143±0.0106</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.7475±0.0000</t>
+          <t>0.7419±0.0057</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.7475±0.0000</t>
+          <t>0.7419±0.0057</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.7475±0.0000</t>
+          <t>0.7419±0.0057</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.6651±0.0000</t>
+          <t>0.7128±0.0132</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.7457±0.0000</t>
+          <t>0.7473±0.0036</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.7431±0.0000</t>
+          <t>0.7434±0.0052</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.7750±0.0000</t>
+          <t>0.8478±0.0058</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.7077±0.0000</t>
+          <t>0.7304±0.0052</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5396±0.0000</t>
+          <t>0.7039±0.0044</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.6795±0.0000</t>
+          <t>0.7854±0.0211</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.7648±0.0000</t>
+          <t>0.7308±0.0096</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.7210±0.0000</t>
+          <t>0.7490±0.0033</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.7092±0.0000</t>
+          <t>0.7543±0.0027</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.7427±0.0000</t>
+          <t>0.7497±0.0036</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.7427±0.0000</t>
+          <t>0.7497±0.0036</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.7427±0.0000</t>
+          <t>0.7497±0.0036</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.7168±0.0000</t>
+          <t>0.7475±0.0063</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.7326±0.0000</t>
+          <t>0.7333±0.0048</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.7207±0.0000</t>
+          <t>0.7323±0.0145</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.8152±0.0000</t>
+          <t>0.8567±0.0053</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.7071±0.0000</t>
+          <t>0.7225±0.0283</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.5363±0.0000</t>
+          <t>0.7178±0.0151</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.6967±0.0000</t>
+          <t>0.7419±0.0139</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.7530±0.0000</t>
+          <t>0.7340±0.0149</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.7233±0.0000</t>
+          <t>0.7405±0.0054</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.7170±0.0000</t>
+          <t>0.7319±0.0302</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.7142±0.0000</t>
+          <t>0.7189±0.0323</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.7142±0.0000</t>
+          <t>0.7188±0.0322</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.7142±0.0000</t>
+          <t>0.7188±0.0323</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.7128±0.0000</t>
+          <t>0.7219±0.0347</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.7302±0.0000</t>
+          <t>0.7450±0.0135</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.7176±0.0000</t>
+          <t>0.7276±0.0136</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.8049±0.0000</t>
+          <t>0.8541±0.0216</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.6779±0.0000</t>
+          <t>0.7093±0.0217</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.6455±0.0000</t>
+          <t>0.6782±0.0324</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.6929±0.0000</t>
+          <t>0.7071±0.0038</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.6643±0.0000</t>
+          <t>0.6772±0.0174</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.7047±0.0000</t>
+          <t>0.7056±0.0061</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.6779±0.0000</t>
+          <t>0.7064±0.0128</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.7060±0.0000</t>
+          <t>0.7090±0.0134</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.7060±0.0000</t>
+          <t>0.7090±0.0134</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.7060±0.0000</t>
+          <t>0.7090±0.0134</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.6650±0.0000</t>
+          <t>0.6927±0.0241</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.7332±0.0000</t>
+          <t>0.7298±0.0120</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.6904±0.0000</t>
+          <t>0.7201±0.0009</t>
         </is>
       </c>
     </row>
